--- a/artfynd/A 19978-2026 artfynd.xlsx
+++ b/artfynd/A 19978-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,218 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132976246</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>431550</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6484628</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132976222</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106160</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>431593</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6484647</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19978-2026 artfynd.xlsx
+++ b/artfynd/A 19978-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>132976246</v>
       </c>
       <c r="B4" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>132976222</v>
       </c>
       <c r="B5" t="n">
-        <v>106170</v>
+        <v>106172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 19978-2026 artfynd.xlsx
+++ b/artfynd/A 19978-2026 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>132976246</v>
       </c>
       <c r="B4" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>132976222</v>
       </c>
       <c r="B5" t="n">
-        <v>106172</v>
+        <v>106180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 19978-2026 artfynd.xlsx
+++ b/artfynd/A 19978-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>129170800</v>
       </c>
       <c r="B2" t="n">
-        <v>88850</v>
+        <v>89164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129282017</v>
+        <v>75452664</v>
       </c>
       <c r="B3" t="n">
-        <v>87066</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,34 +815,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>249255</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brun purpurspindling</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subpurpurascens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch) E.Berger</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ingasäter Norr, Vg</t>
+          <t>Garparör Naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431599</v>
+        <v>431918</v>
       </c>
       <c r="R3" t="n">
-        <v>6484681</v>
+        <v>6484327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,17 +869,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Skifte med mycket blåsippa och hassel, ek och även skogslind</t>
+          <t>Ädellövskog, lövskog och betesmarker</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132976246</v>
+        <v>96603861</v>
       </c>
       <c r="B4" t="n">
-        <v>101348</v>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,34 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ingasäter NO om, Vg</t>
+          <t>Rödegårdens Naturresevat, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431550</v>
+        <v>431919</v>
       </c>
       <c r="R4" t="n">
-        <v>6484628</v>
+        <v>6484346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Västgötabergens svampklubbs utflykt till Garaparör 25/9-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,35 +992,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Lösvkogsområde</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132976222</v>
+        <v>132976244</v>
       </c>
       <c r="B5" t="n">
-        <v>106180</v>
+        <v>99531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>219878</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Storrams</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Polygonatum multiflorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431593</v>
+        <v>431550</v>
       </c>
       <c r="R5" t="n">
-        <v>6484647</v>
+        <v>6484628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,6 +1111,965 @@
           <t>Billingens flora</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132976227</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108274</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>431593</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6484647</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132976237</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104880</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220460</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tandrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cardamine bulbifera</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>431593</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6484647</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>83650942</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SKÖVDE 660389, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>431500</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6484770</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>728DB240-3E51-4B4B-8D87-3C6FECC0A1EE</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2006-05-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2006-05-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>{51ACD733-B7E8-41DA-BE63-130E890B9654}</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Stenström, Skövde Kommun</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132976222</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>431593</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6484647</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132976245</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106679</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221570</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk lungört</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pulmonaria obscura</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Dumort.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>431550</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6484628</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132976239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>431550</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6484628</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132976246</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>431550</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6484628</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132976234</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ingasäter NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>431593</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6484647</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129282017</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87372</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>249255</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brun purpurspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius subpurpurascens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Batsch) E.Berger</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ingasäter Norr, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>431599</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6484681</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Skifte med mycket blåsippa och hassel, ek och även skogslind</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
